--- a/tools/_out/orfs_gen_20261020/out/DesignTable_FS6565_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/DesignTable_FS6565_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BQ4"/>
+  <dimension ref="A1:BO4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,280 +479,270 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>FSWA_CSANG@DRIVE</t>
+          <t>FSWA_MINR@DRIVE</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>FSWA_MINR@DRIVE</t>
+          <t>FSWA_THDL@DRIVE</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>FSWA_THDL@DRIVE</t>
+          <t>FSWA_RELANG@DRIVE</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>FSWA_RELANG@DRIVE</t>
+          <t>FSWA_RELR@DRIVE</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>FSWA_RELR@DRIVE</t>
+          <t>FSWA_STEMR@DRIVE</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>FSWA_STEMR@DRIVE</t>
+          <t>FSWA_HEADL@DRIVE</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>FSWA_HEADL@DRIVE</t>
+          <t>HELIXDIA@HELIXSK_A</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>HELIXDIA@HELIXSK_A</t>
+          <t>HEIGHT@HELIX_A</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>HEIGHT@HELIX_A</t>
+          <t>PITCH@HELIX_A</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>PITCH@HELIX_A</t>
+          <t>PROF_R@THDPROF_A</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>PROF_R@THDPROF_A</t>
+          <t>APEXR@THDPROF_A</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>APEXR@THDPROF_A</t>
+          <t>FSWA_CSR@DRIVE</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>FSWA_CSR@DRIVE</t>
+          <t>FSWB_BODYS@DRIVE</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>FSWB_BODYS@DRIVE</t>
+          <t>FSWB_NECKR@DRIVE</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>FSWB_NECKR@DRIVE</t>
+          <t>FSWB_NUTL@DRIVE</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>FSWB_NUTL@DRIVE</t>
+          <t>FSWB_SKIRTR@DRIVE</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>FSWB_SKIRTR@DRIVE</t>
+          <t>FSWB_SKIRTL@DRIVE</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>FSWB_SKIRTL@DRIVE</t>
+          <t>FSWB_SKIRTFR@DRIVE</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>FSWB_SKIRTFR@DRIVE</t>
+          <t>FSWB_NUTHEXL@DRIVE</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>FSWB_NUTHEXL@DRIVE</t>
+          <t>FSWB_NUTR@DRIVE</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>FSWB_NUTR@DRIVE</t>
+          <t>FSWB_SEAL@DRIVE</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>FSWB_SEAL@DRIVE</t>
+          <t>FSWB_MINR@DRIVE</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>FSWB_CSANG@DRIVE</t>
+          <t>FSWB_THDL@DRIVE</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>FSWB_MINR@DRIVE</t>
+          <t>FSWB_RELANG@DRIVE</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>FSWB_THDL@DRIVE</t>
+          <t>FSWB_RELR@DRIVE</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>FSWB_RELANG@DRIVE</t>
+          <t>FSWB_STEMR@DRIVE</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>FSWB_RELR@DRIVE</t>
+          <t>FSWB_HEADL@DRIVE</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>FSWB_STEMR@DRIVE</t>
+          <t>HELIXDIA@HELIXSK_B</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>FSWB_HEADL@DRIVE</t>
+          <t>HEIGHT@HELIX_B</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>HELIXDIA@HELIXSK_B</t>
+          <t>PITCH@HELIX_B</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>HEIGHT@HELIX_B</t>
+          <t>PROF_R@THDPROF_B</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>PITCH@HELIX_B</t>
+          <t>APEXR@THDPROF_B</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>PROF_R@THDPROF_B</t>
+          <t>FSWB_CSR@DRIVE</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>APEXR@THDPROF_B</t>
+          <t>PROF_AX@THDPROF_B</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>FSWB_CSR@DRIVE</t>
+          <t>DA@BORE_A</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>PROF_AX@THDPROF_B</t>
+          <t>DEPTH@BORECUT_A</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>DA@BORE_A</t>
+          <t>DB@BORE_B</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT_A</t>
+          <t>DEPTH@BORECUT_B</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>DB@BORE_B</t>
+          <t>START@BORECUT_B</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT_B</t>
+          <t>DEPTH@HEXCUT</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>START@BORECUT_B</t>
+          <t>START@HEXCUT</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>DEPTH@HEXCUT</t>
+          <t>NUTHEXA@NUTHEXA</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>START@HEXCUT</t>
+          <t>DEPTH@NUTCUTA</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>NUTHEXA@NUTHEXA</t>
+          <t>NUTHEX@NUTHEX</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>DEPTH@NUTCUTA</t>
+          <t>DEPTH@NUTCUT</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>NUTHEX@NUTHEX</t>
+          <t>$PRP@PartNo</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>DEPTH@NUTCUT</t>
+          <t>$PRP@Description</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>$PRP@PartNo</t>
+          <t>$PRP@GeometryRoot</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>$PRP@Description</t>
+          <t>$PRP@EndA_Thread</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>$PRP@GeometryRoot</t>
+          <t>$PRP@EndB_Thread</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>$PRP@EndA_Thread</t>
+          <t>$PRP@DataStatus</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>$PRP@EndB_Thread</t>
+          <t>$PRP@AxialSource</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>$PRP@DataStatus</t>
+          <t>$COMMENT</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
-        <is>
-          <t>$PRP@AxialSource</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>$COMMENT</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -801,133 +791,133 @@
         <v>0.433</v>
       </c>
       <c r="N2" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="P2" t="n">
         <v>45</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.7448399999999999</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.37242</v>
       </c>
-      <c r="P2" t="n">
+      <c r="X2" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.54271</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>0.36882</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="AK2" t="n">
         <v>45</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AL2" t="n">
         <v>0.4165</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AM2" t="n">
         <v>0.3725</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AN2" t="n">
         <v>0.197</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AO2" t="n">
         <v>0.7448399999999999</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AP2" t="n">
         <v>0.4059</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AQ2" t="n">
         <v>0.0625</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AR2" t="n">
         <v>0.37242</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AS2" t="n">
         <v>0.40625</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AT2" t="n">
         <v>0.4095</v>
       </c>
-      <c r="AA2" t="n">
-        <v>1.288</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.827</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.482</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.54271</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0.37242</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.36882</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0.4165</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.3725</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.7448399999999999</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.4059</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.37242</v>
-      </c>
       <c r="AU2" t="n">
-        <v>0.40625</v>
+        <v>2.986</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.4095</v>
+        <v>0.35</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.986</v>
+        <v>1.493</v>
       </c>
       <c r="AX2" t="n">
         <v>0.35</v>
       </c>
       <c r="AY2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>1.493</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>0.35</v>
-      </c>
       <c r="BA2" t="n">
-        <v>1.08</v>
+        <v>0.41</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.493</v>
+        <v>1.288</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.288</v>
+        <v>0.482</v>
       </c>
       <c r="BE2" t="n">
         <v>0.9399999999999999</v>
@@ -935,53 +925,47 @@
       <c r="BF2" t="n">
         <v>0.482</v>
       </c>
-      <c r="BG2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0.482</v>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>FS6565-08-08</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>ORFS Double Female Swivel Straight (female face-seal swivel x female face-seal swivel), 13/16-16 UN (female O-ring face-seal swivel, SAE J1453) x 13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+        </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>FS6565-08-08</t>
+          <t>FS6565</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>ORFS Double Female Swivel Straight (female face-seal swivel x female face-seal swivel), 13/16-16 UN (female O-ring face-seal swivel, SAE J1453) x 13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>FS6565</t>
+          <t>13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>13/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>Air-Way FF6565 (s523, double-pass 2026-10-15, parts.air-way.com/api/series/523, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p7 FS6565-08-08 (ORFS-p007-t01) | MODEL: L45 seal face -&gt; seal face, body hex S1, nuts S(1) / S(2), bores D19(1) / D19(2): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to nut face) = L45 + the measured seal -&gt; nut face distance SEAL of the swivel at both ends; body hex between the two measured body faces; bore step at the body-hex mid-plane (ASSUMPTION, as 6565); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF6565 = Brennan p7 on overall length, nut hex, body hex (rounding-only differences count as equal) | Air-Way calls it "Male ORFS / Female Double Swivel Union" but prints two nut hexes S(1) / S(2) (= Brennan FFSS-FFSS) | OMi parts file row 5620 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
-        <is>
-          <t>Air-Way FF6565 (s523, double-pass 2026-10-15, parts.air-way.com/api/series/523, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p7 FS6565-08-08 (ORFS-p007-t01) | MODEL: L45 seal face -&gt; seal face, body hex S1, nuts S(1) / S(2), bores D19(1) / D19(2): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to nut face) = L45 + the measured seal -&gt; nut face distance SEAL of the swivel at both ends; body hex between the two measured body faces; bore step at the body-hex mid-plane (ASSUMPTION, as 6565); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>Air-Way FF6565 = Brennan p7 on overall length, nut hex, body hex (rounding-only differences count as equal) | Air-Way calls it "Male ORFS / Female Double Swivel Union" but prints two nut hexes S(1) / S(2) (= Brennan FFSS-FFSS) | OMi parts file row 5620 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
         <is>
           <t>FS6565-08-08</t>
         </is>
@@ -1030,133 +1014,133 @@
         <v>0.325</v>
       </c>
       <c r="N3" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.26238</v>
+      </c>
+      <c r="P3" t="n">
         <v>45</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.50236</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="W3" t="n">
         <v>0.25118</v>
       </c>
-      <c r="P3" t="n">
+      <c r="X3" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>0.26238</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="AK3" t="n">
         <v>45</v>
       </c>
-      <c r="R3" t="n">
+      <c r="AL3" t="n">
         <v>0.2985</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AM3" t="n">
         <v>0.251</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AN3" t="n">
         <v>0.157</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AO3" t="n">
         <v>0.50236</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AP3" t="n">
         <v>0.2947</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AQ3" t="n">
         <v>0.05556</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AR3" t="n">
         <v>0.25118</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AS3" t="n">
         <v>0.28125</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AT3" t="n">
         <v>0.2835</v>
       </c>
-      <c r="AA3" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.39837</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>45</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.25118</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0.26238</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>45</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0.2985</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.50236</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.2947</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0.05556</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.25118</v>
-      </c>
       <c r="AU3" t="n">
-        <v>0.28125</v>
+        <v>2.24</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2835</v>
+        <v>0.16</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.24</v>
+        <v>1.12</v>
       </c>
       <c r="AX3" t="n">
         <v>0.16</v>
       </c>
       <c r="AY3" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.12</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>0.16</v>
-      </c>
       <c r="BA3" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.29</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.12</v>
+        <v>0.975</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.29</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.975</v>
+        <v>0.337</v>
       </c>
       <c r="BE3" t="n">
         <v>0.6899999999999999</v>
@@ -1164,53 +1148,47 @@
       <c r="BF3" t="n">
         <v>0.337</v>
       </c>
-      <c r="BG3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0.337</v>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>FS6565-04-04</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>ORFS Double Female Swivel Straight (female face-seal swivel x female face-seal swivel), 9/16-18 UN (female O-ring face-seal swivel, SAE J1453) x 9/16-18 UN (female O-ring face-seal swivel, SAE J1453)</t>
+        </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>FS6565-04-04</t>
+          <t>FS6565</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>ORFS Double Female Swivel Straight (female face-seal swivel x female face-seal swivel), 9/16-18 UN (female O-ring face-seal swivel, SAE J1453) x 9/16-18 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>9/16-18 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>FS6565</t>
+          <t>9/16-18 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>9/16-18 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>9/16-18 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>Air-Way FF6565 (s523, double-pass 2026-10-15, parts.air-way.com/api/series/523, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6565-04-04 (ORFS-p006-t06) | MODEL: L45 seal face -&gt; seal face, body hex S1, nuts S(1) / S(2), bores D19(1) / D19(2): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to nut face) = L45 + the measured seal -&gt; nut face distance SEAL of the swivel at both ends; body hex between the two measured body faces; bore step at the body-hex mid-plane (ASSUMPTION, as 6565); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF6565 = Brennan p6 on overall length, nut hex, body hex (rounding-only differences count as equal) | Air-Way calls it "Male ORFS / Female Double Swivel Union" but prints two nut hexes S(1) / S(2) (= Brennan FFSS-FFSS) | OMi parts file row 5618 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
-        <is>
-          <t>Air-Way FF6565 (s523, double-pass 2026-10-15, parts.air-way.com/api/series/523, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6565-04-04 (ORFS-p006-t06) | MODEL: L45 seal face -&gt; seal face, body hex S1, nuts S(1) / S(2), bores D19(1) / D19(2): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to nut face) = L45 + the measured seal -&gt; nut face distance SEAL of the swivel at both ends; body hex between the two measured body faces; bore step at the body-hex mid-plane (ASSUMPTION, as 6565); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>Air-Way FF6565 = Brennan p6 on overall length, nut hex, body hex (rounding-only differences count as equal) | Air-Way calls it "Male ORFS / Female Double Swivel Union" but prints two nut hexes S(1) / S(2) (= Brennan FFSS-FFSS) | OMi parts file row 5618 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
         <is>
           <t>FS6565-04-04</t>
         </is>
@@ -1259,133 +1237,133 @@
         <v>0.375</v>
       </c>
       <c r="N4" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.30432</v>
+      </c>
+      <c r="P4" t="n">
         <v>45</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.6198399999999999</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="W4" t="n">
         <v>0.30992</v>
       </c>
-      <c r="P4" t="n">
+      <c r="X4" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.3465</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>0.30432</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="AK4" t="n">
         <v>45</v>
       </c>
-      <c r="R4" t="n">
+      <c r="AL4" t="n">
         <v>0.361</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AM4" t="n">
         <v>0.31</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AN4" t="n">
         <v>0.177</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AO4" t="n">
         <v>0.6198399999999999</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AP4" t="n">
         <v>0.3409</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AQ4" t="n">
         <v>0.0625</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AR4" t="n">
         <v>0.30992</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AS4" t="n">
         <v>0.34375</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AT4" t="n">
         <v>0.3465</v>
       </c>
-      <c r="AA4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0.3575</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.46765</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>45</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.30992</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0.30432</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>45</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.6198399999999999</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.3409</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.30992</v>
-      </c>
       <c r="AU4" t="n">
-        <v>0.34375</v>
+        <v>2.52</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.3465</v>
+        <v>0.26</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="AX4" t="n">
         <v>0.26</v>
       </c>
       <c r="AY4" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.26</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>0.26</v>
-      </c>
       <c r="BA4" t="n">
-        <v>0.905</v>
+        <v>0.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.26</v>
+        <v>1.11</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.11</v>
+        <v>0.392</v>
       </c>
       <c r="BE4" t="n">
         <v>0.8100000000000001</v>
@@ -1393,53 +1371,47 @@
       <c r="BF4" t="n">
         <v>0.392</v>
       </c>
-      <c r="BG4" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0.392</v>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>FS6565-06-06</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>ORFS Double Female Swivel Straight (female face-seal swivel x female face-seal swivel), 11/16-16 UN (female O-ring face-seal swivel, SAE J1453) x 11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+        </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>FS6565-06-06</t>
+          <t>FS6565</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>ORFS Double Female Swivel Straight (female face-seal swivel x female face-seal swivel), 11/16-16 UN (female O-ring face-seal swivel, SAE J1453) x 11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>FS6565</t>
+          <t>11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>11/16-16 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>Air-Way FF6565 (s523, double-pass 2026-10-15, parts.air-way.com/api/series/523, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6565-06-06 (ORFS-p006-t06) | MODEL: L45 seal face -&gt; seal face, body hex S1, nuts S(1) / S(2), bores D19(1) / D19(2): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to nut face) = L45 + the measured seal -&gt; nut face distance SEAL of the swivel at both ends; body hex between the two measured body faces; bore step at the body-hex mid-plane (ASSUMPTION, as 6565); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF6565 = Brennan p6 on overall length, nut hex, body hex (rounding-only differences count as equal) | Air-Way calls it "Male ORFS / Female Double Swivel Union" but prints two nut hexes S(1) / S(2) (= Brennan FFSS-FFSS) | OMi parts file row 5619 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
-        <is>
-          <t>Air-Way FF6565 (s523, double-pass 2026-10-15, parts.air-way.com/api/series/523, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p6 FS6565-06-06 (ORFS-p006-t06) | MODEL: L45 seal face -&gt; seal face, body hex S1, nuts S(1) / S(2), bores D19(1) / D19(2): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to nut face) = L45 + the measured seal -&gt; nut face distance SEAL of the swivel at both ends; body hex between the two measured body faces; bore step at the body-hex mid-plane (ASSUMPTION, as 6565); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>Air-Way FF6565 = Brennan p6 on overall length, nut hex, body hex (rounding-only differences count as equal) | Air-Way calls it "Male ORFS / Female Double Swivel Union" but prints two nut hexes S(1) / S(2) (= Brennan FFSS-FFSS) | OMi parts file row 5619 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
         <is>
           <t>FS6565-06-06</t>
         </is>
